--- a/samples/sample_output.xlsx
+++ b/samples/sample_output.xlsx
@@ -737,12 +737,8 @@
       <c r="K3" s="3" t="n">
         <v>63560</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>18120</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>45440</v>
-      </c>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n">
         <v>142</v>
